--- a/astro-site/public/dl/kit-tareas/07-plantilla-personalizable.xlsx
+++ b/astro-site/public/dl/kit-tareas/07-plantilla-personalizable.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Por Franja Horaria" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Por Área" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Por Perfil" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Franja Horaria" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Área" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Perfil" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Por Franja Horaria'!$A$1:$G$31</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Por Área'!$A$1:$G$31</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Por Perfil'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Por Franja Horaria'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Por Franja Horaria'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Por Área'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Por Área'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Por Perfil'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Por Perfil'!$A$1:$G$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -123,7 +126,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -145,49 +148,108 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -547,15 +609,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -563,6 +626,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -570,9 +634,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -601,9 +663,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" t="inlineStr"/>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -611,9 +671,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="inlineStr"/>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -649,9 +707,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" t="inlineStr"/>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
@@ -659,8 +715,33 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -669,18 +750,18 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -697,10 +778,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -725,7 +807,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -740,18 +822,16 @@
           <t xml:space="preserve">  (Sección 1 — Personaliza este título)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -777,10 +857,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr"/>
       <c r="C7" s="11" t="inlineStr">
@@ -794,10 +872,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr"/>
       <c r="C8" s="11" t="inlineStr">
@@ -811,10 +887,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr"/>
       <c r="C9" s="11" t="inlineStr">
@@ -828,10 +902,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr"/>
       <c r="C10" s="11" t="inlineStr">
@@ -844,24 +916,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  (Sección 2 — Personaliza este título)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="20" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -887,10 +958,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr"/>
       <c r="C14" s="11" t="inlineStr">
@@ -904,10 +973,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr"/>
       <c r="C15" s="11" t="inlineStr">
@@ -921,10 +988,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr"/>
       <c r="C16" s="11" t="inlineStr">
@@ -938,10 +1003,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr"/>
       <c r="C17" s="11" t="inlineStr">
@@ -954,24 +1017,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  (Sección 3 — Personaliza este título)</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="20" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="21" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -997,10 +1059,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr"/>
       <c r="C21" s="11" t="inlineStr">
@@ -1014,10 +1074,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="21" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr"/>
       <c r="C22" s="11" t="inlineStr">
@@ -1031,10 +1089,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr"/>
       <c r="C23" s="11" t="inlineStr">
@@ -1048,10 +1104,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="21" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr"/>
       <c r="C24" s="11" t="inlineStr">
@@ -1064,6 +1118,8 @@
       <c r="F24" s="14" t="n"/>
       <c r="G24" s="15" t="n"/>
     </row>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
@@ -1072,7 +1128,7 @@
       </c>
       <c r="D27" s="16">
         <f>COUNTIF(F5:F25,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E27" s="17" t="inlineStr">
         <is>
@@ -1083,6 +1139,7 @@
         <v>15</v>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
@@ -1090,13 +1147,17 @@
         </is>
       </c>
       <c r="B29" s="15" t="n"/>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="20" t="n"/>
       <c r="E29" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F29" s="15" t="n"/>
-    </row>
+      <c r="G29" s="20" t="n"/>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
@@ -1115,13 +1176,26 @@
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G25">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1130,18 +1204,18 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1158,10 +1232,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1186,7 +1261,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1201,18 +1276,16 @@
           <t xml:space="preserve">  (Sección 1 — Personaliza este título)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1238,10 +1311,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr"/>
       <c r="C7" s="11" t="inlineStr">
@@ -1255,10 +1326,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr"/>
       <c r="C8" s="11" t="inlineStr">
@@ -1272,10 +1341,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr"/>
       <c r="C9" s="11" t="inlineStr">
@@ -1289,10 +1356,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr"/>
       <c r="C10" s="11" t="inlineStr">
@@ -1305,24 +1370,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  (Sección 2 — Personaliza este título)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="20" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1348,10 +1412,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr"/>
       <c r="C14" s="11" t="inlineStr">
@@ -1365,10 +1427,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr"/>
       <c r="C15" s="11" t="inlineStr">
@@ -1382,10 +1442,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr"/>
       <c r="C16" s="11" t="inlineStr">
@@ -1399,10 +1457,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr"/>
       <c r="C17" s="11" t="inlineStr">
@@ -1415,24 +1471,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  (Sección 3 — Personaliza este título)</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="20" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="21" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1458,10 +1513,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr"/>
       <c r="C21" s="11" t="inlineStr">
@@ -1475,10 +1528,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="21" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr"/>
       <c r="C22" s="11" t="inlineStr">
@@ -1492,10 +1543,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr"/>
       <c r="C23" s="11" t="inlineStr">
@@ -1509,10 +1558,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="21" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr"/>
       <c r="C24" s="11" t="inlineStr">
@@ -1525,6 +1572,8 @@
       <c r="F24" s="14" t="n"/>
       <c r="G24" s="15" t="n"/>
     </row>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
@@ -1533,7 +1582,7 @@
       </c>
       <c r="D27" s="16">
         <f>COUNTIF(F5:F25,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E27" s="17" t="inlineStr">
         <is>
@@ -1544,6 +1593,7 @@
         <v>15</v>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
@@ -1551,13 +1601,17 @@
         </is>
       </c>
       <c r="B29" s="15" t="n"/>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="20" t="n"/>
       <c r="E29" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F29" s="15" t="n"/>
-    </row>
+      <c r="G29" s="20" t="n"/>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
@@ -1576,13 +1630,26 @@
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G25">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1591,18 +1658,18 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1619,10 +1686,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1647,7 +1715,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1662,18 +1730,16 @@
           <t xml:space="preserve">  (Sección 1 — Personaliza este título)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1699,10 +1765,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr"/>
       <c r="C7" s="11" t="inlineStr">
@@ -1716,10 +1780,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr"/>
       <c r="C8" s="11" t="inlineStr">
@@ -1733,10 +1795,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr"/>
       <c r="C9" s="11" t="inlineStr">
@@ -1750,10 +1810,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr"/>
       <c r="C10" s="11" t="inlineStr">
@@ -1766,24 +1824,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  (Sección 2 — Personaliza este título)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="20" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1809,10 +1866,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr"/>
       <c r="C14" s="11" t="inlineStr">
@@ -1826,10 +1881,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr"/>
       <c r="C15" s="11" t="inlineStr">
@@ -1843,10 +1896,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr"/>
       <c r="C16" s="11" t="inlineStr">
@@ -1860,10 +1911,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr"/>
       <c r="C17" s="11" t="inlineStr">
@@ -1876,24 +1925,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  (Sección 3 — Personaliza este título)</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="20" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="21" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1919,10 +1967,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr"/>
       <c r="C21" s="11" t="inlineStr">
@@ -1936,10 +1982,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="21" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr"/>
       <c r="C22" s="11" t="inlineStr">
@@ -1953,10 +1997,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr"/>
       <c r="C23" s="11" t="inlineStr">
@@ -1970,10 +2012,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="21" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr"/>
       <c r="C24" s="11" t="inlineStr">
@@ -1986,6 +2026,8 @@
       <c r="F24" s="14" t="n"/>
       <c r="G24" s="15" t="n"/>
     </row>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
@@ -1994,7 +2036,7 @@
       </c>
       <c r="D27" s="16">
         <f>COUNTIF(F5:F25,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E27" s="17" t="inlineStr">
         <is>
@@ -2005,6 +2047,7 @@
         <v>15</v>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
@@ -2012,13 +2055,17 @@
         </is>
       </c>
       <c r="B29" s="15" t="n"/>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="20" t="n"/>
       <c r="E29" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F29" s="15" t="n"/>
-    </row>
+      <c r="G29" s="20" t="n"/>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
@@ -2037,12 +2084,25 @@
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G25">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas/07-plantilla-personalizable.xlsx
+++ b/astro-site/public/dl/kit-tareas/07-plantilla-personalizable.xlsx
@@ -13,12 +13,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Perfil" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$52</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Por Franja Horaria'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Por Franja Horaria'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Por Franja Horaria'!$A$1:$G$35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Por Área'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Por Área'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Por Área'!$A$1:$G$35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Por Perfil'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Por Perfil'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Por Perfil'!$A$1:$G$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -99,8 +100,22 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -123,6 +138,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
         <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -196,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -234,6 +254,57 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -611,123 +682,262 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>Plantilla Maestra Personalizable</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Qué resuelve</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="32" customHeight="1">
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>▸ Tres plantillas maestras ya estructuradas —por franja horaria, por área y por perfil— con las secciones puestas y la zona o el responsable precargados: tú sólo escribes tus tareas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>▸ Escribe en las celdas VERDES de la columna «Tarea», bajo la sección que corresponda. El contador arranca en 0 y sube a medida que escribes: cuenta lo que hay, no un número fijo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>Cómo usar esta plantilla</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>▸ Usa estas hojas en blanco para crear tus propias listas de tareas</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+    <row r="10"/>
+    <row r="11" ht="16" customHeight="1">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>▸ Copia la estructura de las plantillas pre-rellenadas</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="3" t="inlineStr">
+    <row r="12" ht="16" customHeight="1">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>▸ Personaliza: añade tareas, cambia responsables, ajusta horarios</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="3" t="inlineStr">
+    <row r="13" ht="16" customHeight="1">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>▸ Puedes duplicar pestañas (click derecho → 'Mover o copiar')</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="2" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>Consejos de personalización</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>▸ Agrupa las tareas por franja horaria (apertura, servicio, cierre)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+    <row r="18" ht="16" customHeight="1">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>▸ Asigna siempre un responsable — las tareas sin dueño no se hacen</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="3" t="inlineStr">
+    <row r="19" ht="16" customHeight="1">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>▸ Pon hora límite realista — mejor ser específico que genérico</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="3" t="inlineStr">
+    <row r="20" ht="16" customHeight="1">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>▸ Revisa y actualiza las listas cada mes con tu equipo</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>▸ Imprime en A4 y deja espacio para firma del encargado</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes · AI Chef Pro · aichef.pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
     <row r="22"/>
-    <row r="23">
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día (accesos, luces, clima, terraza).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala, barra).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. No se duplican: cada uno cubre un nivel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>▸ Estás en 07-plantilla-personalizable.xlsx: aquí construyes TUS listas cuando ninguna de las otras encaja. Copia la estructura de la que más se parezca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="35" customHeight="1">
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -752,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -802,7 +1012,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -817,372 +1027,362 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (Sección 1 — Personaliza este título)</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="20" t="n"/>
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  APERTURA — escribe aquí abajo tus tareas de apertura</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="27" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="n">
+      <c r="A6" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>(Escribe aquí tu tarea)</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="B6" s="29" t="n"/>
+      <c r="C6" s="30" t="n"/>
+      <c r="D6" s="31" t="inlineStr">
         <is>
           <t>(Responsable)</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>(Hora)</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="33" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr"/>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr"/>
-      <c r="E7" s="13" t="inlineStr"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="B7" s="29" t="inlineStr"/>
+      <c r="C7" s="30" t="n"/>
+      <c r="D7" s="31" t="inlineStr"/>
+      <c r="E7" s="31" t="inlineStr"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="33" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="n">
+      <c r="A8" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr"/>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr"/>
-      <c r="E8" s="13" t="inlineStr"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="B8" s="29" t="inlineStr"/>
+      <c r="C8" s="30" t="n"/>
+      <c r="D8" s="31" t="inlineStr"/>
+      <c r="E8" s="31" t="inlineStr"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="33" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr"/>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="13" t="inlineStr"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="B9" s="29" t="inlineStr"/>
+      <c r="C9" s="30" t="n"/>
+      <c r="D9" s="31" t="inlineStr"/>
+      <c r="E9" s="31" t="inlineStr"/>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="33" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="n">
+      <c r="A10" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr"/>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr"/>
-      <c r="E10" s="13" t="inlineStr"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="29" t="inlineStr"/>
+      <c r="C10" s="30" t="n"/>
+      <c r="D10" s="31" t="inlineStr"/>
+      <c r="E10" s="31" t="inlineStr"/>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="33" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="n"/>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (Sección 2 — Personaliza este título)</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="20" t="n"/>
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SERVICIO — escribe aquí abajo tus tareas de servicio</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="27" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>(Escribe aquí tu tarea)</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="B13" s="29" t="n"/>
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="31" t="inlineStr">
         <is>
           <t>(Responsable)</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t>(Hora)</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="33" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="n">
+      <c r="A14" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr"/>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr"/>
-      <c r="E14" s="13" t="inlineStr"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="B14" s="29" t="inlineStr"/>
+      <c r="C14" s="30" t="n"/>
+      <c r="D14" s="31" t="inlineStr"/>
+      <c r="E14" s="31" t="inlineStr"/>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="33" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr"/>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="13" t="inlineStr"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="B15" s="29" t="inlineStr"/>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="31" t="inlineStr"/>
+      <c r="E15" s="31" t="inlineStr"/>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="33" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="n">
+      <c r="A16" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr"/>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="13" t="inlineStr"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="B16" s="29" t="inlineStr"/>
+      <c r="C16" s="30" t="n"/>
+      <c r="D16" s="31" t="inlineStr"/>
+      <c r="E16" s="31" t="inlineStr"/>
+      <c r="F16" s="32" t="n"/>
+      <c r="G16" s="33" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr"/>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="13" t="inlineStr"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18"/>
+      <c r="B17" s="29" t="inlineStr"/>
+      <c r="C17" s="30" t="n"/>
+      <c r="D17" s="31" t="inlineStr"/>
+      <c r="E17" s="31" t="inlineStr"/>
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="33" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="34" t="n"/>
+      <c r="F18" s="34" t="n"/>
+      <c r="G18" s="34" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (Sección 3 — Personaliza este título)</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="19" t="n"/>
-      <c r="F19" s="19" t="n"/>
-      <c r="G19" s="20" t="n"/>
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CIERRE — escribe aquí abajo tus tareas de cierre</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="26" t="n"/>
+      <c r="G19" s="27" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="28" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>(Escribe aquí tu tarea)</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="B20" s="29" t="n"/>
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="31" t="inlineStr">
         <is>
           <t>(Responsable)</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>(Hora)</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="33" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="inlineStr"/>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="13" t="inlineStr"/>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="B21" s="29" t="inlineStr"/>
+      <c r="C21" s="30" t="n"/>
+      <c r="D21" s="31" t="inlineStr"/>
+      <c r="E21" s="31" t="inlineStr"/>
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="33" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="n">
+      <c r="A22" s="28" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr"/>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="13" t="inlineStr"/>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="B22" s="29" t="inlineStr"/>
+      <c r="C22" s="30" t="n"/>
+      <c r="D22" s="31" t="inlineStr"/>
+      <c r="E22" s="31" t="inlineStr"/>
+      <c r="F22" s="32" t="n"/>
+      <c r="G22" s="33" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="n">
+      <c r="A23" s="28" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="10" t="inlineStr"/>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr"/>
-      <c r="E23" s="13" t="inlineStr"/>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="B23" s="29" t="inlineStr"/>
+      <c r="C23" s="30" t="n"/>
+      <c r="D23" s="31" t="inlineStr"/>
+      <c r="E23" s="31" t="inlineStr"/>
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="33" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="n">
+      <c r="A24" s="28" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="10" t="inlineStr"/>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr"/>
-      <c r="E24" s="13" t="inlineStr"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="15" t="n"/>
-    </row>
-    <row r="25"/>
-    <row r="26"/>
+      <c r="B24" s="29" t="inlineStr"/>
+      <c r="C24" s="30" t="n"/>
+      <c r="D24" s="31" t="inlineStr"/>
+      <c r="E24" s="31" t="inlineStr"/>
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="33" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="n"/>
+      <c r="B25" s="29" t="n"/>
+      <c r="C25" s="30" t="n"/>
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="31" t="n"/>
+      <c r="F25" s="32" t="n"/>
+      <c r="G25" s="33" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="n"/>
+      <c r="B26" s="29" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="32" t="n"/>
+      <c r="G26" s="33" t="n"/>
+    </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D27" s="16">
-        <f>COUNTIF(F5:F25,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28"/>
+      <c r="A27" s="35" t="n"/>
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="31" t="n"/>
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="33" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="n"/>
+      <c r="B28" s="29" t="n"/>
+      <c r="C28" s="30" t="n"/>
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="31" t="n"/>
+      <c r="F28" s="32" t="n"/>
+      <c r="G28" s="33" t="n"/>
+    </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="20" t="n"/>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="20" t="n"/>
+      <c r="A29" s="35" t="n"/>
+      <c r="B29" s="29" t="n"/>
+      <c r="C29" s="30" t="n"/>
+      <c r="D29" s="31" t="n"/>
+      <c r="E29" s="31" t="n"/>
+      <c r="F29" s="32" t="n"/>
+      <c r="G29" s="33" t="n"/>
     </row>
     <row r="30"/>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D31" s="16">
+        <f>COUNTIFS(B5:B29,"?*",F5:F29,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F31" s="16">
+        <f>COUNTIF(B5:B29,"?*")-COUNTIF(F5:F29,"N/A")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B33" s="36" t="n"/>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F33" s="36" t="n"/>
+      <c r="G33" s="20" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
-    <mergeCell ref="F29:G29"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="F33:G33"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A31:C31"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G25">
+  <conditionalFormatting sqref="A5:G29">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1206,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1228,7 +1428,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+          <t>Fecha: ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1456,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1271,372 +1471,422 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (Sección 1 — Personaliza este título)</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="20" t="n"/>
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  COCINA — escribe aquí abajo tus tareas de cocina</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="27" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="n">
+      <c r="A6" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>(Escribe aquí tu tarea)</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="B6" s="29" t="n"/>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
         <is>
           <t>(Responsable)</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>(Hora)</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="33" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr"/>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr"/>
-      <c r="E7" s="13" t="inlineStr"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="B7" s="29" t="inlineStr"/>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr"/>
+      <c r="E7" s="31" t="inlineStr"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="33" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="n">
+      <c r="A8" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr"/>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr"/>
-      <c r="E8" s="13" t="inlineStr"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="B8" s="29" t="inlineStr"/>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr"/>
+      <c r="E8" s="31" t="inlineStr"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="33" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr"/>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="13" t="inlineStr"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="B9" s="29" t="inlineStr"/>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr"/>
+      <c r="E9" s="31" t="inlineStr"/>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="33" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="n">
+      <c r="A10" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr"/>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr"/>
-      <c r="E10" s="13" t="inlineStr"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="29" t="inlineStr"/>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr"/>
+      <c r="E10" s="31" t="inlineStr"/>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="33" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="n"/>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (Sección 2 — Personaliza este título)</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="20" t="n"/>
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SALA — escribe aquí abajo tus tareas de sala</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="27" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>(Escribe aquí tu tarea)</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="B13" s="29" t="n"/>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
         <is>
           <t>(Responsable)</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t>(Hora)</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="33" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="n">
+      <c r="A14" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr"/>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr"/>
-      <c r="E14" s="13" t="inlineStr"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="B14" s="29" t="inlineStr"/>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="inlineStr"/>
+      <c r="E14" s="31" t="inlineStr"/>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="33" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr"/>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="13" t="inlineStr"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="B15" s="29" t="inlineStr"/>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr"/>
+      <c r="E15" s="31" t="inlineStr"/>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="33" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="n">
+      <c r="A16" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr"/>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="13" t="inlineStr"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="B16" s="29" t="inlineStr"/>
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr"/>
+      <c r="E16" s="31" t="inlineStr"/>
+      <c r="F16" s="32" t="n"/>
+      <c r="G16" s="33" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr"/>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="13" t="inlineStr"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18"/>
+      <c r="B17" s="29" t="inlineStr"/>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr"/>
+      <c r="E17" s="31" t="inlineStr"/>
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="33" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="34" t="n"/>
+      <c r="F18" s="34" t="n"/>
+      <c r="G18" s="34" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (Sección 3 — Personaliza este título)</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="19" t="n"/>
-      <c r="F19" s="19" t="n"/>
-      <c r="G19" s="20" t="n"/>
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BARRA — escribe aquí abajo tus tareas de barra</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="26" t="n"/>
+      <c r="G19" s="27" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="28" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>(Escribe aquí tu tarea)</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="B20" s="29" t="n"/>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>Barra</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
         <is>
           <t>(Responsable)</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>(Hora)</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="33" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="inlineStr"/>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="13" t="inlineStr"/>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="B21" s="29" t="inlineStr"/>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>Barra</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr"/>
+      <c r="E21" s="31" t="inlineStr"/>
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="33" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="n">
+      <c r="A22" s="28" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr"/>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="13" t="inlineStr"/>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="B22" s="29" t="inlineStr"/>
+      <c r="C22" s="30" t="inlineStr">
+        <is>
+          <t>Barra</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr"/>
+      <c r="E22" s="31" t="inlineStr"/>
+      <c r="F22" s="32" t="n"/>
+      <c r="G22" s="33" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="n">
+      <c r="A23" s="28" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="10" t="inlineStr"/>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr"/>
-      <c r="E23" s="13" t="inlineStr"/>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="B23" s="29" t="inlineStr"/>
+      <c r="C23" s="30" t="inlineStr">
+        <is>
+          <t>Barra</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr"/>
+      <c r="E23" s="31" t="inlineStr"/>
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="33" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="n">
+      <c r="A24" s="28" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="10" t="inlineStr"/>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr"/>
-      <c r="E24" s="13" t="inlineStr"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="15" t="n"/>
-    </row>
-    <row r="25"/>
-    <row r="26"/>
+      <c r="B24" s="29" t="inlineStr"/>
+      <c r="C24" s="30" t="inlineStr">
+        <is>
+          <t>Barra</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="inlineStr"/>
+      <c r="E24" s="31" t="inlineStr"/>
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="33" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="n"/>
+      <c r="B25" s="29" t="n"/>
+      <c r="C25" s="30" t="n"/>
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="31" t="n"/>
+      <c r="F25" s="32" t="n"/>
+      <c r="G25" s="33" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="n"/>
+      <c r="B26" s="29" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="32" t="n"/>
+      <c r="G26" s="33" t="n"/>
+    </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D27" s="16">
-        <f>COUNTIF(F5:F25,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28"/>
+      <c r="A27" s="35" t="n"/>
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="31" t="n"/>
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="33" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="n"/>
+      <c r="B28" s="29" t="n"/>
+      <c r="C28" s="30" t="n"/>
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="31" t="n"/>
+      <c r="F28" s="32" t="n"/>
+      <c r="G28" s="33" t="n"/>
+    </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="20" t="n"/>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="20" t="n"/>
+      <c r="A29" s="35" t="n"/>
+      <c r="B29" s="29" t="n"/>
+      <c r="C29" s="30" t="n"/>
+      <c r="D29" s="31" t="n"/>
+      <c r="E29" s="31" t="n"/>
+      <c r="F29" s="32" t="n"/>
+      <c r="G29" s="33" t="n"/>
     </row>
     <row r="30"/>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D31" s="16">
+        <f>COUNTIFS(B5:B29,"?*",F5:F29,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F31" s="16">
+        <f>COUNTIF(B5:B29,"?*")-COUNTIF(F5:F29,"N/A")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B33" s="36" t="n"/>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F33" s="36" t="n"/>
+      <c r="G33" s="20" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
-    <mergeCell ref="F29:G29"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="F33:G33"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A31:C31"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G25">
+  <conditionalFormatting sqref="A5:G29">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1660,7 +1910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1682,7 +1932,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+          <t>Fecha: ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1960,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1725,372 +1975,410 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (Sección 1 — Personaliza este título)</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="20" t="n"/>
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  COCINA — escribe aquí abajo tus tareas de cocina</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="27" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="n">
+      <c r="A6" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>(Escribe aquí tu tarea)</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>(Responsable)</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="B6" s="29" t="n"/>
+      <c r="C6" s="30" t="n"/>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>Jefe de Cocina</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>(Hora)</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="33" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr"/>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr"/>
-      <c r="E7" s="13" t="inlineStr"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="B7" s="29" t="inlineStr"/>
+      <c r="C7" s="30" t="n"/>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>Jefe de Cocina</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="33" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="n">
+      <c r="A8" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr"/>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr"/>
-      <c r="E8" s="13" t="inlineStr"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="B8" s="29" t="inlineStr"/>
+      <c r="C8" s="30" t="n"/>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>Jefe de Cocina</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="33" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr"/>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="13" t="inlineStr"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="B9" s="29" t="inlineStr"/>
+      <c r="C9" s="30" t="n"/>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>Jefe de Cocina</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr"/>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="33" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="n">
+      <c r="A10" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr"/>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr"/>
-      <c r="E10" s="13" t="inlineStr"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="29" t="inlineStr"/>
+      <c r="C10" s="30" t="n"/>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>Jefe de Cocina</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr"/>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="33" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="n"/>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (Sección 2 — Personaliza este título)</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="20" t="n"/>
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SALA — escribe aquí abajo tus tareas de sala</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="27" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>(Escribe aquí tu tarea)</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>(Responsable)</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="B13" s="29" t="n"/>
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>Jefe de Sala</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t>(Hora)</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="33" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="n">
+      <c r="A14" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr"/>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr"/>
-      <c r="E14" s="13" t="inlineStr"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="B14" s="29" t="inlineStr"/>
+      <c r="C14" s="30" t="n"/>
+      <c r="D14" s="31" t="inlineStr">
+        <is>
+          <t>Jefe de Sala</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="inlineStr"/>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="33" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr"/>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="13" t="inlineStr"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="B15" s="29" t="inlineStr"/>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>Jefe de Sala</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="inlineStr"/>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="33" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="n">
+      <c r="A16" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr"/>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="13" t="inlineStr"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="B16" s="29" t="inlineStr"/>
+      <c r="C16" s="30" t="n"/>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>Jefe de Sala</t>
+        </is>
+      </c>
+      <c r="E16" s="31" t="inlineStr"/>
+      <c r="F16" s="32" t="n"/>
+      <c r="G16" s="33" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr"/>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="13" t="inlineStr"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18"/>
+      <c r="B17" s="29" t="inlineStr"/>
+      <c r="C17" s="30" t="n"/>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>Jefe de Sala</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr"/>
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="33" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="34" t="n"/>
+      <c r="F18" s="34" t="n"/>
+      <c r="G18" s="34" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (Sección 3 — Personaliza este título)</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="19" t="n"/>
-      <c r="F19" s="19" t="n"/>
-      <c r="G19" s="20" t="n"/>
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GERENCIA — escribe aquí abajo tus tareas de gerencia</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="26" t="n"/>
+      <c r="G19" s="27" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="28" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>(Escribe aquí tu tarea)</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>(Responsable)</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="B20" s="29" t="n"/>
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>(Hora)</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="33" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="inlineStr"/>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="13" t="inlineStr"/>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="B21" s="29" t="inlineStr"/>
+      <c r="C21" s="30" t="n"/>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr"/>
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="33" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="n">
+      <c r="A22" s="28" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr"/>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="13" t="inlineStr"/>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="B22" s="29" t="inlineStr"/>
+      <c r="C22" s="30" t="n"/>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr"/>
+      <c r="F22" s="32" t="n"/>
+      <c r="G22" s="33" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="n">
+      <c r="A23" s="28" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="10" t="inlineStr"/>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr"/>
-      <c r="E23" s="13" t="inlineStr"/>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="B23" s="29" t="inlineStr"/>
+      <c r="C23" s="30" t="n"/>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr"/>
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="33" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="n">
+      <c r="A24" s="28" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="10" t="inlineStr"/>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr"/>
-      <c r="E24" s="13" t="inlineStr"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="15" t="n"/>
-    </row>
-    <row r="25"/>
-    <row r="26"/>
+      <c r="B24" s="29" t="inlineStr"/>
+      <c r="C24" s="30" t="n"/>
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr"/>
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="33" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="n"/>
+      <c r="B25" s="29" t="n"/>
+      <c r="C25" s="30" t="n"/>
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="31" t="n"/>
+      <c r="F25" s="32" t="n"/>
+      <c r="G25" s="33" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="n"/>
+      <c r="B26" s="29" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="32" t="n"/>
+      <c r="G26" s="33" t="n"/>
+    </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D27" s="16">
-        <f>COUNTIF(F5:F25,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28"/>
+      <c r="A27" s="35" t="n"/>
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="31" t="n"/>
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="33" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="n"/>
+      <c r="B28" s="29" t="n"/>
+      <c r="C28" s="30" t="n"/>
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="31" t="n"/>
+      <c r="F28" s="32" t="n"/>
+      <c r="G28" s="33" t="n"/>
+    </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="20" t="n"/>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="20" t="n"/>
+      <c r="A29" s="35" t="n"/>
+      <c r="B29" s="29" t="n"/>
+      <c r="C29" s="30" t="n"/>
+      <c r="D29" s="31" t="n"/>
+      <c r="E29" s="31" t="n"/>
+      <c r="F29" s="32" t="n"/>
+      <c r="G29" s="33" t="n"/>
     </row>
     <row r="30"/>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D31" s="16">
+        <f>COUNTIFS(B5:B29,"?*",F5:F29,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F31" s="16">
+        <f>COUNTIF(B5:B29,"?*")-COUNTIF(F5:F29,"N/A")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B33" s="36" t="n"/>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F33" s="36" t="n"/>
+      <c r="G33" s="20" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
-    <mergeCell ref="F29:G29"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="F33:G33"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A31:C31"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G25">
+  <conditionalFormatting sqref="A5:G29">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/astro-site/public/dl/kit-tareas/07-plantilla-personalizable.xlsx
+++ b/astro-site/public/dl/kit-tareas/07-plantilla-personalizable.xlsx
@@ -808,6 +808,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="32" customHeight="1">
       <c r="B25" s="24" t="inlineStr">
         <is>
@@ -829,6 +830,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="23" t="inlineStr">
         <is>
@@ -836,6 +838,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="32" customHeight="1">
       <c r="B31" s="24" t="inlineStr">
         <is>
@@ -850,6 +853,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="23" t="inlineStr">
         <is>
@@ -857,6 +861,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36" ht="32" customHeight="1">
       <c r="B36" s="24" t="inlineStr">
         <is>
@@ -871,6 +876,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="23" t="inlineStr">
         <is>
@@ -878,10 +884,11 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="32" customHeight="1">
+    <row r="40"/>
+    <row r="41" ht="16" customHeight="1">
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día (accesos, luces, clima, terraza).</t>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
         </is>
       </c>
     </row>
@@ -899,10 +906,10 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1">
+    <row r="44" ht="48" customHeight="1">
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>▸ Orden de uso: local → áreas → caja. No se duplican: cada uno cubre un nivel.</t>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
         </is>
       </c>
     </row>
@@ -913,6 +920,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="23" t="inlineStr">
         <is>
@@ -920,6 +928,7 @@
         </is>
       </c>
     </row>
+    <row r="48"/>
     <row r="49" ht="35" customHeight="1">
       <c r="B49" s="23" t="inlineStr">
         <is>
@@ -934,6 +943,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="23" t="inlineStr">
         <is>
@@ -1382,7 +1392,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1886,7 +1896,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2378,7 +2388,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
